--- a/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
@@ -48,12 +48,12 @@
     <t xml:space="preserve">Toltén</t>
   </si>
   <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
     <t xml:space="preserve">Traiguén</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -574,7 +574,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>131.19</v>
+        <v>141.27</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>127.15</v>
+        <v>136.79</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>122.02</v>
+        <v>130.89</v>
       </c>
     </row>
     <row r="5">
@@ -625,7 +625,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>117</v>
+        <v>127.68</v>
       </c>
     </row>
     <row r="6">
@@ -636,13 +636,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>9211</v>
+        <v>9206</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>115.34</v>
+        <v>124.37</v>
       </c>
     </row>
     <row r="7">
@@ -653,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>9206</v>
+        <v>9211</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>114.83</v>
+        <v>124.26</v>
       </c>
     </row>
     <row r="8">
@@ -676,7 +676,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>114.31</v>
+        <v>123.74</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>113.91</v>
+        <v>123.09</v>
       </c>
     </row>
     <row r="10">
@@ -710,7 +710,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>113.75</v>
+        <v>123.04</v>
       </c>
     </row>
     <row r="11">
@@ -727,7 +727,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>113.72</v>
+        <v>121.99</v>
       </c>
     </row>
     <row r="12">
@@ -744,7 +744,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>111.02</v>
+        <v>120.26</v>
       </c>
     </row>
     <row r="13">
@@ -761,7 +761,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>108.32</v>
+        <v>116.57</v>
       </c>
     </row>
     <row r="14">
@@ -778,7 +778,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>106.91</v>
+        <v>115.4</v>
       </c>
     </row>
     <row r="15">
@@ -795,7 +795,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>105.51</v>
+        <v>113.93</v>
       </c>
     </row>
     <row r="16">
@@ -812,7 +812,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>104.68</v>
+        <v>112.96</v>
       </c>
     </row>
     <row r="17">
@@ -829,7 +829,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>104.31</v>
+        <v>112.73</v>
       </c>
     </row>
     <row r="18">
@@ -846,7 +846,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>104.29</v>
+        <v>110.92</v>
       </c>
     </row>
     <row r="19">
@@ -863,7 +863,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>99.38</v>
+        <v>106.61</v>
       </c>
     </row>
     <row r="20">
@@ -880,7 +880,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>94.3</v>
+        <v>101.23</v>
       </c>
     </row>
     <row r="21">
@@ -897,7 +897,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>92.16</v>
+        <v>98.59</v>
       </c>
     </row>
     <row r="22">
@@ -914,7 +914,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>91.6</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="23">
@@ -931,7 +931,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>91.11</v>
+        <v>98.04</v>
       </c>
     </row>
     <row r="24">
@@ -948,7 +948,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>90.32</v>
+        <v>97.97</v>
       </c>
     </row>
     <row r="25">
@@ -965,7 +965,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>85.45</v>
+        <v>91.52</v>
       </c>
     </row>
     <row r="26">
@@ -982,7 +982,7 @@
         <v>2020</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>84.15</v>
+        <v>90.53</v>
       </c>
     </row>
     <row r="27">
@@ -999,7 +999,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>82.95</v>
+        <v>89.98</v>
       </c>
     </row>
     <row r="28">
@@ -1016,7 +1016,7 @@
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>82.55</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="29">
@@ -1033,7 +1033,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>80.9</v>
+        <v>86.95</v>
       </c>
     </row>
     <row r="30">
@@ -1050,7 +1050,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>80.61</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="31">
@@ -1067,7 +1067,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>76.19</v>
+        <v>81.81</v>
       </c>
     </row>
     <row r="32">
@@ -1084,7 +1084,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>73.83</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="33">
@@ -1101,7 +1101,7 @@
         <v>2020</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>73.13</v>
+        <v>78.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_la araucania.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:11</t>
+    <t xml:space="preserve">2026-10-05 16:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
